--- a/public/purchase_import_template.xlsx
+++ b/public/purchase_import_template.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.###"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,27 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E2EC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -63,13 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,120 +413,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Rate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>itemA</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" t="n">
         <v>50000</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Deskripsi item A</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>itemB</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>200</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" t="n">
         <v>75000</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Petunjuk</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Isi sheet 'Data' mulai baris 2. Baris contoh boleh dihapus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Item Code: kode item persis seperti di ERPNext.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Qty: angka lebih dari 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Rate: harga beli per unit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Item yang sama boleh di beberapa baris dengan rate berbeda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Hanya sheet pertama yang dibaca.</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Deskripsi item B</t>
         </is>
       </c>
     </row>
